--- a/output/yearly_benthic_cover_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_85_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.02050506606869</v>
+        <v>45.20465067323496</v>
       </c>
       <c r="M2" t="n">
-        <v>100.6073370734078</v>
+        <v>99.59073738348715</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01856603653681</v>
+        <v>88.04793011037086</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94197164216495</v>
+        <v>45.9458280698657</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228698106778945</v>
+        <v>2.228770501915401</v>
       </c>
       <c r="E3" t="n">
-        <v>5.713387556863602</v>
+        <v>5.717234208278215</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428993689263151</v>
+        <v>0.7429235006384669</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97784214267489</v>
+        <v>33.97886607591511</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17337097061049</v>
+        <v>34.17448102936947</v>
       </c>
       <c r="I3" t="n">
-        <v>6.539246834893103</v>
+        <v>6.562382915263773</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643121055789469</v>
+        <v>4.643271878990419</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98143396346317</v>
+        <v>11.95206988962915</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84186554294052</v>
+        <v>48.86655036177918</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652711485687</v>
+        <v>106.764448321274</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.06430426490077</v>
+        <v>87.18830622746214</v>
       </c>
       <c r="C4" t="n">
-        <v>42.6167941306762</v>
+        <v>42.7196124754029</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182517681353199</v>
+        <v>2.187645793492946</v>
       </c>
       <c r="E4" t="n">
-        <v>6.505129113272068</v>
+        <v>6.52509290760671</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744452550101195</v>
+        <v>0.7444800176506348</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27379380143707</v>
+        <v>33.35189665098027</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24481730465497</v>
+        <v>34.2460808119292</v>
       </c>
       <c r="I4" t="n">
-        <v>5.460765375949806</v>
+        <v>5.480109935485904</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652828438132468</v>
+        <v>4.653000110316468</v>
       </c>
       <c r="K4" t="n">
-        <v>12.93569573509922</v>
+        <v>12.81169377253786</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26586438881088</v>
+        <v>44.28640533774637</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8183542545863</v>
+        <v>99.81771158568714</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.84996609315733</v>
+        <v>86.07131767774658</v>
       </c>
       <c r="C5" t="n">
-        <v>42.24999460996867</v>
+        <v>42.45325319994358</v>
       </c>
       <c r="D5" t="n">
-        <v>2.123108278440844</v>
+        <v>2.133327819758394</v>
       </c>
       <c r="E5" t="n">
-        <v>7.087837799829317</v>
+        <v>7.125553531645344</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457702482693845</v>
+        <v>0.7457990338667606</v>
       </c>
       <c r="G5" t="n">
-        <v>32.36806174746052</v>
+        <v>32.52378843909607</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30543142039168</v>
+        <v>34.30675555787099</v>
       </c>
       <c r="I5" t="n">
-        <v>4.55869254708193</v>
+        <v>4.574849333841775</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661064051683653</v>
+        <v>4.661243961667254</v>
       </c>
       <c r="K5" t="n">
-        <v>14.15003390684267</v>
+        <v>13.92868232225343</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44828355607894</v>
+        <v>43.46583920181725</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84831207289028</v>
+        <v>99.84777472401426</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.44711477126631</v>
+        <v>84.7187867673187</v>
       </c>
       <c r="C6" t="n">
-        <v>41.55507849475929</v>
+        <v>41.81133365475005</v>
       </c>
       <c r="D6" t="n">
-        <v>2.054556705153116</v>
+        <v>2.067371757642332</v>
       </c>
       <c r="E6" t="n">
-        <v>7.493086106067076</v>
+        <v>7.541603180455866</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468902269686085</v>
+        <v>0.7469194215334894</v>
       </c>
       <c r="G6" t="n">
-        <v>31.32295181143208</v>
+        <v>31.51825099160634</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35695044055599</v>
+        <v>34.35829339054051</v>
       </c>
       <c r="I6" t="n">
-        <v>3.804615562535645</v>
+        <v>3.81810164095586</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668063918553803</v>
+        <v>4.668246384584309</v>
       </c>
       <c r="K6" t="n">
-        <v>15.55288522873371</v>
+        <v>15.2812132326813</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76540592797694</v>
+        <v>42.78037396440639</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87336965146993</v>
+        <v>99.87292085183773</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.78256458156312</v>
+        <v>83.14559931664843</v>
       </c>
       <c r="C7" t="n">
-        <v>40.48135348804766</v>
+        <v>40.83124979514496</v>
       </c>
       <c r="D7" t="n">
-        <v>1.973399422637852</v>
+        <v>1.990830668124858</v>
       </c>
       <c r="E7" t="n">
-        <v>7.726195135961509</v>
+        <v>7.793356727685103</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478449578548766</v>
+        <v>0.7478733895122828</v>
       </c>
       <c r="G7" t="n">
-        <v>30.08566026187471</v>
+        <v>30.35133881837731</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40086806132432</v>
+        <v>34.402175917565</v>
       </c>
       <c r="I7" t="n">
-        <v>3.174565755316882</v>
+        <v>3.185815110932104</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674030986592978</v>
+        <v>4.674208684451767</v>
       </c>
       <c r="K7" t="n">
-        <v>17.21743541843687</v>
+        <v>16.85440068335157</v>
       </c>
       <c r="L7" t="n">
-        <v>42.1955273278895</v>
+        <v>42.20829114258803</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89431623437403</v>
+        <v>99.89394162108456</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.76390853156643</v>
+        <v>88.00812602140924</v>
       </c>
       <c r="C8" t="n">
-        <v>42.85017482266134</v>
+        <v>43.13781520426495</v>
       </c>
       <c r="D8" t="n">
-        <v>1.977643629685282</v>
+        <v>1.99506754747461</v>
       </c>
       <c r="E8" t="n">
-        <v>9.605441845178568</v>
+        <v>9.628249163488547</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494533544136784</v>
+        <v>0.749465011226267</v>
       </c>
       <c r="G8" t="n">
-        <v>30.60979423153858</v>
+        <v>30.85683924002303</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47485430302921</v>
+        <v>34.47539051640828</v>
       </c>
       <c r="I8" t="n">
-        <v>5.662637702635621</v>
+        <v>5.618958222624346</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684083465085489</v>
+        <v>4.684156320164169</v>
       </c>
       <c r="K8" t="n">
-        <v>12.23609146843359</v>
+        <v>11.99187397859076</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72538420371191</v>
+        <v>44.68340997149502</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81165049480686</v>
+        <v>99.81309915435072</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.67381086287057</v>
+        <v>85.87360272349807</v>
       </c>
       <c r="C9" t="n">
-        <v>41.63871285081966</v>
+        <v>41.8755085285547</v>
       </c>
       <c r="D9" t="n">
-        <v>1.883135013579287</v>
+        <v>1.89827057212857</v>
       </c>
       <c r="E9" t="n">
-        <v>9.934336291439598</v>
+        <v>9.942936286867269</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508318674810898</v>
+        <v>0.7508297045430623</v>
       </c>
       <c r="G9" t="n">
-        <v>29.14699818037522</v>
+        <v>29.35972265820402</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53826590413013</v>
+        <v>34.53816640898086</v>
       </c>
       <c r="I9" t="n">
-        <v>4.727544434108427</v>
+        <v>4.690991439380158</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69269917175681</v>
+        <v>4.69268565339414</v>
       </c>
       <c r="K9" t="n">
-        <v>14.32618913712943</v>
+        <v>14.1263972765019</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87780252031105</v>
+        <v>43.84201202209273</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84270450826014</v>
+        <v>99.84391782714934</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.30323857894396</v>
+        <v>83.51096686902522</v>
       </c>
       <c r="C10" t="n">
-        <v>40.00133246257475</v>
+        <v>40.24064995607282</v>
       </c>
       <c r="D10" t="n">
-        <v>1.776961133628208</v>
+        <v>1.792212151474326</v>
       </c>
       <c r="E10" t="n">
-        <v>10.03186412954287</v>
+        <v>10.03995851045511</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520173607693947</v>
+        <v>0.7520030833747287</v>
       </c>
       <c r="G10" t="n">
-        <v>27.50364820099406</v>
+        <v>27.71936334289096</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59279859539216</v>
+        <v>34.59214183523751</v>
       </c>
       <c r="I10" t="n">
-        <v>3.945840653808558</v>
+        <v>3.915268674500538</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700108504808716</v>
+        <v>4.700019271092054</v>
       </c>
       <c r="K10" t="n">
-        <v>16.69676142105604</v>
+        <v>16.48903313097479</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17058543764396</v>
+        <v>43.14001159519179</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86867932127475</v>
+        <v>99.8696946822394</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.87962231249952</v>
+        <v>80.99653931966276</v>
       </c>
       <c r="C11" t="n">
-        <v>38.18890798263016</v>
+        <v>38.33289685473554</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6696740906532</v>
+        <v>1.680531558725209</v>
       </c>
       <c r="E11" t="n">
-        <v>9.974950431660028</v>
+        <v>9.95884316368203</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530378648414381</v>
+        <v>0.753014187224713</v>
       </c>
       <c r="G11" t="n">
-        <v>25.8430687821946</v>
+        <v>25.99204834493406</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63974178270615</v>
+        <v>34.63865261233678</v>
       </c>
       <c r="I11" t="n">
-        <v>3.292662705185104</v>
+        <v>3.267110782605513</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706486655258987</v>
+        <v>4.706338670154456</v>
       </c>
       <c r="K11" t="n">
-        <v>19.12037768750049</v>
+        <v>19.00346068033723</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58110764504134</v>
+        <v>42.55488500174668</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89039331517199</v>
+        <v>99.89124253681945</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.30443994916897</v>
+        <v>78.42247080861191</v>
       </c>
       <c r="C12" t="n">
-        <v>36.12286307062777</v>
+        <v>36.26413412998813</v>
       </c>
       <c r="D12" t="n">
-        <v>1.556795778187507</v>
+        <v>1.567393504025437</v>
       </c>
       <c r="E12" t="n">
-        <v>9.758442985614453</v>
+        <v>9.742677273629733</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539184730733917</v>
+        <v>0.7538866097467308</v>
       </c>
       <c r="G12" t="n">
-        <v>24.09594818578663</v>
+        <v>24.24219141892729</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68024976137602</v>
+        <v>34.67878404834961</v>
       </c>
       <c r="I12" t="n">
-        <v>2.747094308422279</v>
+        <v>2.725746643016043</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711990456708696</v>
+        <v>4.711791310917067</v>
       </c>
       <c r="K12" t="n">
-        <v>21.69556005083103</v>
+        <v>21.5775291913881</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09011402561939</v>
+        <v>42.06758360132917</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90853714707819</v>
+        <v>99.90924692270539</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.71199216681521</v>
+        <v>75.76898459284162</v>
       </c>
       <c r="C13" t="n">
-        <v>33.95419851647796</v>
+        <v>34.03123851320003</v>
       </c>
       <c r="D13" t="n">
-        <v>1.444278639903355</v>
+        <v>1.451860017642052</v>
       </c>
       <c r="E13" t="n">
-        <v>9.43507906193768</v>
+        <v>9.403493476071946</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546790947789058</v>
+        <v>0.754640714625758</v>
       </c>
       <c r="G13" t="n">
-        <v>22.35441781160716</v>
+        <v>22.45528539627952</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71523835982967</v>
+        <v>34.71347287278486</v>
       </c>
       <c r="I13" t="n">
-        <v>2.29155485639028</v>
+        <v>2.273727649026496</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716744342368159</v>
+        <v>4.716504466410987</v>
       </c>
       <c r="K13" t="n">
-        <v>24.28800783318481</v>
+        <v>24.23101540715839</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68148547510328</v>
+        <v>41.66203089511338</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92369182476604</v>
+        <v>99.92428481547179</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.90675145145063</v>
+        <v>82.86946467364332</v>
       </c>
       <c r="C14" t="n">
-        <v>38.4741818173443</v>
+        <v>38.48136342203226</v>
       </c>
       <c r="D14" t="n">
-        <v>1.445966257685972</v>
+        <v>1.453552550030305</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93377638418823</v>
+        <v>11.86658823258035</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555609259057605</v>
+        <v>0.7555204508506543</v>
       </c>
       <c r="G14" t="n">
-        <v>24.38383475007101</v>
+        <v>24.45056254228582</v>
       </c>
       <c r="H14" t="n">
-        <v>36.75909873045999</v>
+        <v>36.72304022519752</v>
       </c>
       <c r="I14" t="n">
-        <v>2.906258616228665</v>
+        <v>2.898197854882076</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722255786911001</v>
+        <v>4.722002817816588</v>
       </c>
       <c r="K14" t="n">
-        <v>17.09324854854938</v>
+        <v>17.13053532635668</v>
       </c>
       <c r="L14" t="n">
-        <v>44.33580741209405</v>
+        <v>44.29160714621778</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90323777798773</v>
+        <v>99.90350589460671</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.01956568607686</v>
+        <v>81.91130836672956</v>
       </c>
       <c r="C15" t="n">
-        <v>38.00657257538674</v>
+        <v>37.97059494867811</v>
       </c>
       <c r="D15" t="n">
-        <v>1.410049480875093</v>
+        <v>1.418072983361313</v>
       </c>
       <c r="E15" t="n">
-        <v>12.07045016338509</v>
+        <v>11.97986178108516</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563053346320632</v>
+        <v>0.7562637351210832</v>
       </c>
       <c r="G15" t="n">
-        <v>23.80721318600544</v>
+        <v>23.85375208380237</v>
       </c>
       <c r="H15" t="n">
-        <v>36.82437086472474</v>
+        <v>36.75916851018436</v>
       </c>
       <c r="I15" t="n">
-        <v>2.424268315004037</v>
+        <v>2.417540928668487</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726908341450392</v>
+        <v>4.726648344506769</v>
       </c>
       <c r="K15" t="n">
-        <v>17.98043431392314</v>
+        <v>18.08869163327044</v>
       </c>
       <c r="L15" t="n">
-        <v>43.93226370468377</v>
+        <v>43.86020792208251</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91927059399366</v>
+        <v>99.91949450403106</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.31574415128776</v>
+        <v>79.2604324856305</v>
       </c>
       <c r="C16" t="n">
-        <v>35.67690056274803</v>
+        <v>35.69284427569704</v>
       </c>
       <c r="D16" t="n">
-        <v>1.308914706357267</v>
+        <v>1.318278084312157</v>
       </c>
       <c r="E16" t="n">
-        <v>11.54169593992254</v>
+        <v>11.47285009330553</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569479998963077</v>
+        <v>0.7569050278073355</v>
       </c>
       <c r="G16" t="n">
-        <v>22.09965811781719</v>
+        <v>22.17507770732276</v>
       </c>
       <c r="H16" t="n">
-        <v>36.85566212097897</v>
+        <v>36.79033936345094</v>
       </c>
       <c r="I16" t="n">
-        <v>2.021940266963555</v>
+        <v>2.016325785635947</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73092499935192</v>
+        <v>4.730656423795845</v>
       </c>
       <c r="K16" t="n">
-        <v>20.68425584871224</v>
+        <v>20.7395675143695</v>
       </c>
       <c r="L16" t="n">
-        <v>43.57150280201183</v>
+        <v>43.5004342952482</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93265921347211</v>
+        <v>99.93284608531474</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.1949368844177</v>
+        <v>81.01389279027754</v>
       </c>
       <c r="C17" t="n">
-        <v>37.0366465239776</v>
+        <v>36.9680636193794</v>
       </c>
       <c r="D17" t="n">
-        <v>1.30999425850525</v>
+        <v>1.319365142202229</v>
       </c>
       <c r="E17" t="n">
-        <v>12.38389593578116</v>
+        <v>12.27231133412802</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575723070686778</v>
+        <v>0.7575291750129244</v>
       </c>
       <c r="G17" t="n">
-        <v>22.61573069698935</v>
+        <v>22.64934199543251</v>
       </c>
       <c r="H17" t="n">
-        <v>37.38390499340239</v>
+        <v>37.27665546042243</v>
       </c>
       <c r="I17" t="n">
-        <v>2.009011773491643</v>
+        <v>2.004132339248638</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734826919179234</v>
+        <v>4.734557343830776</v>
       </c>
       <c r="K17" t="n">
-        <v>18.80506311558229</v>
+        <v>18.98610720972245</v>
       </c>
       <c r="L17" t="n">
-        <v>44.09137848815529</v>
+        <v>43.97907980141271</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93308812771519</v>
+        <v>99.93325063051456</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.57968862750576</v>
+        <v>78.55718697012442</v>
       </c>
       <c r="C18" t="n">
-        <v>34.73097435441743</v>
+        <v>34.82019354040709</v>
       </c>
       <c r="D18" t="n">
-        <v>1.216504136420645</v>
+        <v>1.230800249329518</v>
       </c>
       <c r="E18" t="n">
-        <v>11.77932440146363</v>
+        <v>11.72705822040215</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581107036653457</v>
+        <v>0.7580663864023746</v>
       </c>
       <c r="G18" t="n">
-        <v>21.00171795596662</v>
+        <v>21.12896186464124</v>
       </c>
       <c r="H18" t="n">
-        <v>37.41047323914052</v>
+        <v>37.30309067181031</v>
       </c>
       <c r="I18" t="n">
-        <v>1.675366292940582</v>
+        <v>1.67129466252398</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738191897908409</v>
+        <v>4.73791491501484</v>
       </c>
       <c r="K18" t="n">
-        <v>21.42031137249424</v>
+        <v>21.44281302987558</v>
       </c>
       <c r="L18" t="n">
-        <v>43.79290839049133</v>
+        <v>43.6813230869604</v>
       </c>
       <c r="M18" t="n">
-        <v>99.944194117403</v>
+        <v>99.94432965724307</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.53618899266181</v>
+        <v>77.58261584159564</v>
       </c>
       <c r="C19" t="n">
-        <v>33.94011311998469</v>
+        <v>34.09057897512463</v>
       </c>
       <c r="D19" t="n">
-        <v>1.179679167559566</v>
+        <v>1.195834755301126</v>
       </c>
       <c r="E19" t="n">
-        <v>11.65634481549075</v>
+        <v>11.62808576827616</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758567497122697</v>
+        <v>0.7585240222132369</v>
       </c>
       <c r="G19" t="n">
-        <v>20.36597197976864</v>
+        <v>20.52871451312609</v>
       </c>
       <c r="H19" t="n">
-        <v>37.43301461644786</v>
+        <v>37.32561011133892</v>
       </c>
       <c r="I19" t="n">
-        <v>1.40156405925544</v>
+        <v>1.405071532507382</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741046857016855</v>
+        <v>4.740775138832729</v>
       </c>
       <c r="K19" t="n">
-        <v>22.46381100733818</v>
+        <v>22.41738415840435</v>
       </c>
       <c r="L19" t="n">
-        <v>43.5493852037859</v>
+        <v>43.44522940583729</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95330933110877</v>
+        <v>99.95319253936627</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.857863445752</v>
+        <v>75.02969874642632</v>
       </c>
       <c r="C20" t="n">
-        <v>31.47689958792843</v>
+        <v>31.75339078770665</v>
       </c>
       <c r="D20" t="n">
-        <v>1.085081605590868</v>
+        <v>1.10487649456836</v>
       </c>
       <c r="E20" t="n">
-        <v>10.91639448900903</v>
+        <v>10.93887411138123</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589622208037755</v>
+        <v>0.7589188048519038</v>
       </c>
       <c r="G20" t="n">
-        <v>18.73284040519445</v>
+        <v>18.96724779800019</v>
       </c>
       <c r="H20" t="n">
-        <v>37.45249303778719</v>
+        <v>37.34503665870998</v>
       </c>
       <c r="I20" t="n">
-        <v>1.168577807343102</v>
+        <v>1.171502348590271</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743513880023595</v>
+        <v>4.743242530324398</v>
       </c>
       <c r="K20" t="n">
-        <v>25.14213655424799</v>
+        <v>24.97030125357367</v>
       </c>
       <c r="L20" t="n">
-        <v>43.34203152284425</v>
+        <v>43.23727819392781</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96106766502066</v>
+        <v>99.96097023520812</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.36365022739254</v>
+        <v>81.34799135150978</v>
       </c>
       <c r="C21" t="n">
-        <v>35.58694078811136</v>
+        <v>35.74699986074581</v>
       </c>
       <c r="D21" t="n">
-        <v>1.085799835459617</v>
+        <v>1.105603338777998</v>
       </c>
       <c r="E21" t="n">
-        <v>13.10644524423575</v>
+        <v>13.06970691429925</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594645879376616</v>
+        <v>0.7594180604172123</v>
       </c>
       <c r="G21" t="n">
-        <v>20.65878658734803</v>
+        <v>20.83578775018302</v>
       </c>
       <c r="H21" t="n">
-        <v>39.39083000565132</v>
+        <v>39.22566645938269</v>
       </c>
       <c r="I21" t="n">
-        <v>1.615670292149789</v>
+        <v>1.605445950842036</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746653674610384</v>
+        <v>4.746362877607576</v>
       </c>
       <c r="K21" t="n">
-        <v>18.63634977260748</v>
+        <v>18.65200864849022</v>
       </c>
       <c r="L21" t="n">
-        <v>45.72288938708067</v>
+        <v>45.54751180740406</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94617994779949</v>
+        <v>99.94652031664009</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_85_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.20465067323496</v>
+        <v>45.09455354050084</v>
       </c>
       <c r="M2" t="n">
-        <v>99.59073738348715</v>
+        <v>100.0354992924626</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04793011037086</v>
+        <v>87.93495058456611</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9458280698657</v>
+        <v>45.85663792718105</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228770501915401</v>
+        <v>2.228548160333664</v>
       </c>
       <c r="E3" t="n">
-        <v>5.717234208278215</v>
+        <v>5.660263859824817</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429235006384669</v>
+        <v>0.7428493867778881</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97886607591511</v>
+        <v>33.94905779794124</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17448102936947</v>
+        <v>34.17107179178285</v>
       </c>
       <c r="I3" t="n">
-        <v>6.562382915263773</v>
+        <v>6.540350920543853</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643271878990419</v>
+        <v>4.642808667361801</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95206988962915</v>
+        <v>12.06504941543387</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86655036177918</v>
+        <v>48.8435283781146</v>
       </c>
       <c r="M3" t="n">
-        <v>106.764448321274</v>
+        <v>106.7652157207295</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.18830622746214</v>
+        <v>87.00820004793424</v>
       </c>
       <c r="C4" t="n">
-        <v>42.7196124754029</v>
+        <v>42.56235074054348</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187645793492946</v>
+        <v>2.183743335029682</v>
       </c>
       <c r="E4" t="n">
-        <v>6.52509290760671</v>
+        <v>6.456747376160617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444800176506348</v>
+        <v>0.7444037299373932</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35189665098027</v>
+        <v>33.26651405446486</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2460808119292</v>
+        <v>34.24257157712008</v>
       </c>
       <c r="I4" t="n">
-        <v>5.480109935485904</v>
+        <v>5.4616966631129</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653000110316468</v>
+        <v>4.652523312108707</v>
       </c>
       <c r="K4" t="n">
-        <v>12.81169377253786</v>
+        <v>12.99179995206576</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28640533774637</v>
+        <v>44.26417289293119</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81771158568714</v>
+        <v>99.81832358554043</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.07131767774658</v>
+        <v>85.84669401436027</v>
       </c>
       <c r="C5" t="n">
-        <v>42.45325319994358</v>
+        <v>42.24847144300647</v>
       </c>
       <c r="D5" t="n">
-        <v>2.133327819758394</v>
+        <v>2.126977036595971</v>
       </c>
       <c r="E5" t="n">
-        <v>7.125553531645344</v>
+        <v>7.048816498287361</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457990338667606</v>
+        <v>0.7457216171168399</v>
       </c>
       <c r="G5" t="n">
-        <v>32.52378843909607</v>
+        <v>32.40175269063025</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30675555787099</v>
+        <v>34.30319438737462</v>
       </c>
       <c r="I5" t="n">
-        <v>4.574849333841775</v>
+        <v>4.559471677374974</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661243961667254</v>
+        <v>4.660760106980248</v>
       </c>
       <c r="K5" t="n">
-        <v>13.92868232225343</v>
+        <v>14.15330598563973</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46583920181725</v>
+        <v>43.4465087751562</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84777472401426</v>
+        <v>99.8482862038024</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.7187867673187</v>
+        <v>84.30158337034005</v>
       </c>
       <c r="C6" t="n">
-        <v>41.81133365475005</v>
+        <v>41.41141715380118</v>
       </c>
       <c r="D6" t="n">
-        <v>2.067371757642332</v>
+        <v>2.051015395260415</v>
       </c>
       <c r="E6" t="n">
-        <v>7.541603180455866</v>
+        <v>7.431291873615173</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469194215334894</v>
+        <v>0.74684365102908</v>
       </c>
       <c r="G6" t="n">
-        <v>31.51825099160634</v>
+        <v>31.2445750275991</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35829339054051</v>
+        <v>34.35480794733767</v>
       </c>
       <c r="I6" t="n">
-        <v>3.81810164095586</v>
+        <v>3.805276656566869</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668246384584309</v>
+        <v>4.667772818931749</v>
       </c>
       <c r="K6" t="n">
-        <v>15.2812132326813</v>
+        <v>15.69841662965994</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78037396440639</v>
+        <v>42.76351422550069</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87292085183773</v>
+        <v>99.87334800896181</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.14559931664843</v>
+        <v>82.70315969932382</v>
       </c>
       <c r="C7" t="n">
-        <v>40.83124979514496</v>
+        <v>40.40381292323293</v>
       </c>
       <c r="D7" t="n">
-        <v>1.990830668124858</v>
+        <v>1.973040126302264</v>
       </c>
       <c r="E7" t="n">
-        <v>7.793356727685103</v>
+        <v>7.677956863886289</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478733895122828</v>
+        <v>0.7477994064061476</v>
       </c>
       <c r="G7" t="n">
-        <v>30.35133881837731</v>
+        <v>30.05672234405022</v>
       </c>
       <c r="H7" t="n">
-        <v>34.402175917565</v>
+        <v>34.39877269468278</v>
       </c>
       <c r="I7" t="n">
-        <v>3.185815110932104</v>
+        <v>3.175121973957701</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674208684451767</v>
+        <v>4.673746290038422</v>
       </c>
       <c r="K7" t="n">
-        <v>16.85440068335157</v>
+        <v>17.29684030067618</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20829114258803</v>
+        <v>42.19364464674181</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89394162108456</v>
+        <v>99.89429787065092</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.00812602140924</v>
+        <v>87.52253766730965</v>
       </c>
       <c r="C8" t="n">
-        <v>43.13781520426495</v>
+        <v>42.66053956364673</v>
       </c>
       <c r="D8" t="n">
-        <v>1.99506754747461</v>
+        <v>1.977259242740332</v>
       </c>
       <c r="E8" t="n">
-        <v>9.628249163488547</v>
+        <v>9.479460531955487</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749465011226267</v>
+        <v>0.7493984883132442</v>
       </c>
       <c r="G8" t="n">
-        <v>30.85683924002303</v>
+        <v>30.54564589426372</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47539051640828</v>
+        <v>34.47233046240922</v>
       </c>
       <c r="I8" t="n">
-        <v>5.618958222624346</v>
+        <v>5.614702495669865</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684156320164169</v>
+        <v>4.683740551957776</v>
       </c>
       <c r="K8" t="n">
-        <v>11.99187397859076</v>
+        <v>12.47746233269036</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68340997149502</v>
+        <v>44.67524071272931</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81309915435072</v>
+        <v>99.81324260906639</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.87360272349807</v>
+        <v>85.45228152579402</v>
       </c>
       <c r="C9" t="n">
-        <v>41.8755085285547</v>
+        <v>41.46132780682243</v>
       </c>
       <c r="D9" t="n">
-        <v>1.89827057212857</v>
+        <v>1.883239249555929</v>
       </c>
       <c r="E9" t="n">
-        <v>9.942936286867269</v>
+        <v>9.809951561792758</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508297045430623</v>
+        <v>0.7507687602997646</v>
       </c>
       <c r="G9" t="n">
-        <v>29.35972265820402</v>
+        <v>29.0931800988268</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53816640898086</v>
+        <v>34.53536297378916</v>
       </c>
       <c r="I9" t="n">
-        <v>4.690991439380158</v>
+        <v>4.687474129656093</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69268565339414</v>
+        <v>4.692304751873528</v>
       </c>
       <c r="K9" t="n">
-        <v>14.1263972765019</v>
+        <v>14.54771847420597</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84201202209273</v>
+        <v>43.83498976075855</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84391782714934</v>
+        <v>99.84403604178696</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.51096686902522</v>
+        <v>83.18552819764213</v>
       </c>
       <c r="C10" t="n">
-        <v>40.24064995607282</v>
+        <v>39.9214244158867</v>
       </c>
       <c r="D10" t="n">
-        <v>1.792212151474326</v>
+        <v>1.781364196001497</v>
       </c>
       <c r="E10" t="n">
-        <v>10.03995851045511</v>
+        <v>9.931334563870561</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520030833747287</v>
+        <v>0.7519457566534395</v>
       </c>
       <c r="G10" t="n">
-        <v>27.71936334289096</v>
+        <v>27.51936557614436</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59214183523751</v>
+        <v>34.5895048060582</v>
       </c>
       <c r="I10" t="n">
-        <v>3.915268674500538</v>
+        <v>3.912352319830068</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700019271092054</v>
+        <v>4.699660979083997</v>
       </c>
       <c r="K10" t="n">
-        <v>16.48903313097479</v>
+        <v>16.81447180235786</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14001159519179</v>
+        <v>43.13389616704276</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8696946822394</v>
+        <v>99.86979238528733</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.99653931966276</v>
+        <v>80.82537020631086</v>
       </c>
       <c r="C11" t="n">
-        <v>38.33289685473554</v>
+        <v>38.16723436798165</v>
       </c>
       <c r="D11" t="n">
-        <v>1.680531558725209</v>
+        <v>1.676453409853105</v>
       </c>
       <c r="E11" t="n">
-        <v>9.95884316368203</v>
+        <v>9.890557307539392</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753014187224713</v>
+        <v>0.7529581717330103</v>
       </c>
       <c r="G11" t="n">
-        <v>25.99204834493406</v>
+        <v>25.89865360529711</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63865261233678</v>
+        <v>34.63607589971846</v>
       </c>
       <c r="I11" t="n">
-        <v>3.267110782605513</v>
+        <v>3.264683238838487</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706338670154456</v>
+        <v>4.705988573331314</v>
       </c>
       <c r="K11" t="n">
-        <v>19.00346068033723</v>
+        <v>19.17462979368913</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55488500174668</v>
+        <v>42.54945938500059</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89124253681945</v>
+        <v>99.89132354667137</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.42247080861191</v>
+        <v>78.4078925355647</v>
       </c>
       <c r="C12" t="n">
-        <v>36.26413412998813</v>
+        <v>36.25457305129289</v>
       </c>
       <c r="D12" t="n">
-        <v>1.567393504025437</v>
+        <v>1.570095953906091</v>
       </c>
       <c r="E12" t="n">
-        <v>9.742677273629733</v>
+        <v>9.717034432979</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538866097467308</v>
+        <v>0.7538300426866247</v>
       </c>
       <c r="G12" t="n">
-        <v>24.24219141892729</v>
+        <v>24.25559278790539</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67878404834961</v>
+        <v>34.67618196358472</v>
       </c>
       <c r="I12" t="n">
-        <v>2.725746643016043</v>
+        <v>2.723719587711453</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711791310917067</v>
+        <v>4.711437766791404</v>
       </c>
       <c r="K12" t="n">
-        <v>21.5775291913881</v>
+        <v>21.59210746443531</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06758360132917</v>
+        <v>42.0626338387485</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90924692270539</v>
+        <v>99.90931435447672</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.76898459284162</v>
+        <v>75.98678349851339</v>
       </c>
       <c r="C13" t="n">
-        <v>34.03123851320003</v>
+        <v>34.25373856760797</v>
       </c>
       <c r="D13" t="n">
-        <v>1.451860017642052</v>
+        <v>1.464602005730952</v>
       </c>
       <c r="E13" t="n">
-        <v>9.403493476071946</v>
+        <v>9.442823258616047</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754640714625758</v>
+        <v>0.7545813678065227</v>
       </c>
       <c r="G13" t="n">
-        <v>22.45528539627952</v>
+        <v>22.62587185132268</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71347287278486</v>
+        <v>34.71074291910003</v>
       </c>
       <c r="I13" t="n">
-        <v>2.273727649026496</v>
+        <v>2.272028547146407</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716504466410987</v>
+        <v>4.716133548790767</v>
       </c>
       <c r="K13" t="n">
-        <v>24.23101540715839</v>
+        <v>24.01321650148659</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66203089511338</v>
+        <v>41.657386053469</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92428481547179</v>
+        <v>99.92434112256356</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.86946467364332</v>
+        <v>83.0214784881689</v>
       </c>
       <c r="C14" t="n">
-        <v>38.48136342203226</v>
+        <v>38.70288086546518</v>
       </c>
       <c r="D14" t="n">
-        <v>1.453552550030305</v>
+        <v>1.466265400630639</v>
       </c>
       <c r="E14" t="n">
-        <v>11.86658823258035</v>
+        <v>11.89928140074587</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555204508506543</v>
+        <v>0.7554383697727204</v>
       </c>
       <c r="G14" t="n">
-        <v>24.45056254228582</v>
+        <v>24.62585178230633</v>
       </c>
       <c r="H14" t="n">
-        <v>36.72304022519752</v>
+        <v>36.72444802103038</v>
       </c>
       <c r="I14" t="n">
-        <v>2.898197854882076</v>
+        <v>2.828703702603452</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722002817816588</v>
+        <v>4.721489811079502</v>
       </c>
       <c r="K14" t="n">
-        <v>17.13053532635668</v>
+        <v>16.9785215118311</v>
       </c>
       <c r="L14" t="n">
-        <v>44.29160714621778</v>
+        <v>44.22441446607851</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90350589460671</v>
+        <v>99.90581684337479</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.91130836672956</v>
+        <v>82.24192172361172</v>
       </c>
       <c r="C15" t="n">
-        <v>37.97059494867811</v>
+        <v>38.36015570314886</v>
       </c>
       <c r="D15" t="n">
-        <v>1.418072983361313</v>
+        <v>1.437552124179329</v>
       </c>
       <c r="E15" t="n">
-        <v>11.97986178108516</v>
+        <v>12.05951386535697</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562637351210832</v>
+        <v>0.75616081658195</v>
       </c>
       <c r="G15" t="n">
-        <v>23.85375208380237</v>
+        <v>24.14361378516732</v>
       </c>
       <c r="H15" t="n">
-        <v>36.75916851018436</v>
+        <v>36.75956863623225</v>
       </c>
       <c r="I15" t="n">
-        <v>2.417540928668487</v>
+        <v>2.359507392456706</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726648344506769</v>
+        <v>4.726005103637188</v>
       </c>
       <c r="K15" t="n">
-        <v>18.08869163327044</v>
+        <v>17.75807827638828</v>
       </c>
       <c r="L15" t="n">
-        <v>43.86020792208251</v>
+        <v>43.80319091761275</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91949450403106</v>
+        <v>99.9214248971499</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.2604324856305</v>
+        <v>79.72356214763188</v>
       </c>
       <c r="C16" t="n">
-        <v>35.69284427569704</v>
+        <v>36.20619037536918</v>
       </c>
       <c r="D16" t="n">
-        <v>1.318278084312157</v>
+        <v>1.342475989947784</v>
       </c>
       <c r="E16" t="n">
-        <v>11.47285009330553</v>
+        <v>11.58990650648105</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569050278073355</v>
+        <v>0.7567829786102045</v>
       </c>
       <c r="G16" t="n">
-        <v>22.17507770732276</v>
+        <v>22.54681501421243</v>
       </c>
       <c r="H16" t="n">
-        <v>36.79033936345094</v>
+        <v>36.78981406455775</v>
       </c>
       <c r="I16" t="n">
-        <v>2.016325785635947</v>
+        <v>1.967873977508881</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730656423795845</v>
+        <v>4.729893616313778</v>
       </c>
       <c r="K16" t="n">
-        <v>20.7395675143695</v>
+        <v>20.27643785236812</v>
       </c>
       <c r="L16" t="n">
-        <v>43.5004342952482</v>
+        <v>43.45182990025002</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93284608531474</v>
+        <v>99.93445812798731</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.01389279027754</v>
+        <v>81.49025641133217</v>
       </c>
       <c r="C17" t="n">
-        <v>36.9680636193794</v>
+        <v>37.49675206848495</v>
       </c>
       <c r="D17" t="n">
-        <v>1.319365142202229</v>
+        <v>1.343542396920096</v>
       </c>
       <c r="E17" t="n">
-        <v>12.27231133412802</v>
+        <v>12.39183074495198</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575291750129244</v>
+        <v>0.7573841354658651</v>
       </c>
       <c r="G17" t="n">
-        <v>22.64934199543251</v>
+        <v>23.03378064813388</v>
       </c>
       <c r="H17" t="n">
-        <v>37.27665546042243</v>
+        <v>37.28809374327974</v>
       </c>
       <c r="I17" t="n">
-        <v>2.004132339248638</v>
+        <v>1.941973895918949</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734557343830776</v>
+        <v>4.733650846661657</v>
       </c>
       <c r="K17" t="n">
-        <v>18.98610720972245</v>
+        <v>18.50974358866781</v>
       </c>
       <c r="L17" t="n">
-        <v>43.97907980141271</v>
+        <v>43.92882325960657</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93325063051456</v>
+        <v>99.93531891675934</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.55718697012442</v>
+        <v>79.07588355218616</v>
       </c>
       <c r="C18" t="n">
-        <v>34.82019354040709</v>
+        <v>35.38188366298122</v>
       </c>
       <c r="D18" t="n">
-        <v>1.230800249329518</v>
+        <v>1.256178311139898</v>
       </c>
       <c r="E18" t="n">
-        <v>11.72705822040215</v>
+        <v>11.85595244206007</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580663864023746</v>
+        <v>0.7579011579195762</v>
       </c>
       <c r="G18" t="n">
-        <v>21.12896186464124</v>
+        <v>21.53600492256032</v>
       </c>
       <c r="H18" t="n">
-        <v>37.30309067181031</v>
+        <v>37.31354817362571</v>
       </c>
       <c r="I18" t="n">
-        <v>1.67129466252398</v>
+        <v>1.619416307883237</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73791491501484</v>
+        <v>4.736882236997351</v>
       </c>
       <c r="K18" t="n">
-        <v>21.44281302987558</v>
+        <v>20.92411644781383</v>
       </c>
       <c r="L18" t="n">
-        <v>43.6813230869604</v>
+        <v>43.64005616987386</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94432965724307</v>
+        <v>99.94605628066891</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.58261584159564</v>
+        <v>78.12278324594929</v>
       </c>
       <c r="C19" t="n">
-        <v>34.09057897512463</v>
+        <v>34.67495575816586</v>
       </c>
       <c r="D19" t="n">
-        <v>1.195834755301126</v>
+        <v>1.222206515046623</v>
       </c>
       <c r="E19" t="n">
-        <v>11.62808576827616</v>
+        <v>11.76083955261178</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585240222132369</v>
+        <v>0.7583387240143187</v>
       </c>
       <c r="G19" t="n">
-        <v>20.52871451312609</v>
+        <v>20.95359017984032</v>
       </c>
       <c r="H19" t="n">
-        <v>37.32561011133892</v>
+        <v>37.33509074996922</v>
       </c>
       <c r="I19" t="n">
-        <v>1.405071532507382</v>
+        <v>1.353100499377545</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740775138832729</v>
+        <v>4.739617025089491</v>
       </c>
       <c r="K19" t="n">
-        <v>22.41738415840435</v>
+        <v>21.87721675405071</v>
       </c>
       <c r="L19" t="n">
-        <v>43.44522940583729</v>
+        <v>43.40275016271374</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95319253936627</v>
+        <v>99.9549226749303</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.02969874642632</v>
+        <v>75.60043777429023</v>
       </c>
       <c r="C20" t="n">
-        <v>31.75339078770665</v>
+        <v>32.36056012476751</v>
       </c>
       <c r="D20" t="n">
-        <v>1.10487649456836</v>
+        <v>1.13192859514554</v>
       </c>
       <c r="E20" t="n">
-        <v>10.93887411138123</v>
+        <v>11.08015274939551</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589188048519038</v>
+        <v>0.7587159333630649</v>
       </c>
       <c r="G20" t="n">
-        <v>18.96724779800019</v>
+        <v>19.40585948735289</v>
       </c>
       <c r="H20" t="n">
-        <v>37.34503665870998</v>
+        <v>37.35366179852734</v>
       </c>
       <c r="I20" t="n">
-        <v>1.171502348590271</v>
+        <v>1.128144626986721</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743242530324398</v>
+        <v>4.741974583519155</v>
       </c>
       <c r="K20" t="n">
-        <v>24.97030125357367</v>
+        <v>24.39956222570979</v>
       </c>
       <c r="L20" t="n">
-        <v>43.23727819392781</v>
+        <v>43.20229152454</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96097023520812</v>
+        <v>99.96241387501729</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.34799135150978</v>
+        <v>81.55749631159605</v>
       </c>
       <c r="C21" t="n">
-        <v>35.74699986074581</v>
+        <v>36.11951680255538</v>
       </c>
       <c r="D21" t="n">
-        <v>1.105603338777998</v>
+        <v>1.132645352603428</v>
       </c>
       <c r="E21" t="n">
-        <v>13.06970691429925</v>
+        <v>13.08889311034654</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594180604172123</v>
+        <v>0.7591963658797353</v>
       </c>
       <c r="G21" t="n">
-        <v>20.83578775018302</v>
+        <v>21.16165349862098</v>
       </c>
       <c r="H21" t="n">
-        <v>39.22566645938269</v>
+        <v>39.12082067964183</v>
       </c>
       <c r="I21" t="n">
-        <v>1.605445950842036</v>
+        <v>1.549310017755192</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746362877607576</v>
+        <v>4.744977286748345</v>
       </c>
       <c r="K21" t="n">
-        <v>18.65200864849022</v>
+        <v>18.44250368840395</v>
       </c>
       <c r="L21" t="n">
-        <v>45.54751180740406</v>
+        <v>45.38636852278296</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94652031664009</v>
+        <v>99.94838901374229</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_85_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.09455354050084</v>
+        <v>44.04400691358234</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0354992924626</v>
+        <v>92.82203734934112</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.93495058456611</v>
+        <v>81.54338428331152</v>
       </c>
       <c r="C3" t="n">
-        <v>45.85663792718105</v>
+        <v>43.29893983886708</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228548160333664</v>
+        <v>2.183400161711428</v>
       </c>
       <c r="E3" t="n">
-        <v>5.660263859824817</v>
+        <v>4.162887714471225</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428493867778881</v>
+        <v>0.7376798660328503</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94905779794124</v>
+        <v>32.84197743240939</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17107179178285</v>
+        <v>33.93327383751111</v>
       </c>
       <c r="I3" t="n">
-        <v>6.540350920543853</v>
+        <v>3.073666108470209</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642808667361801</v>
+        <v>4.610499162705314</v>
       </c>
       <c r="K3" t="n">
-        <v>12.06504941543387</v>
+        <v>18.45661571668847</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8435283781146</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652157207295</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.00820004793424</v>
+        <v>88.72834910884869</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56235074054348</v>
+        <v>42.9535821181904</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183743335029682</v>
+        <v>2.1891552297654</v>
       </c>
       <c r="E4" t="n">
-        <v>6.456747376160617</v>
+        <v>6.587393052468161</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444037299373932</v>
+        <v>0.7396242635397811</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26651405446486</v>
+        <v>33.55062784206228</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24257157712008</v>
+        <v>34.02271612282993</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4616966631129</v>
+        <v>7.016180951059507</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652523312108707</v>
+        <v>4.622651647123631</v>
       </c>
       <c r="K4" t="n">
-        <v>12.99179995206576</v>
+        <v>11.27165089115132</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26417289293119</v>
+        <v>45.54150911999886</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81832358554043</v>
+        <v>99.76674212934059</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.84669401436027</v>
+        <v>87.67470874938803</v>
       </c>
       <c r="C5" t="n">
-        <v>42.24847144300647</v>
+        <v>42.98762960491099</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126977036595971</v>
+        <v>2.139416861473108</v>
       </c>
       <c r="E5" t="n">
-        <v>7.048816498287361</v>
+        <v>7.414365761938868</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457216171168399</v>
+        <v>0.7412720524480096</v>
       </c>
       <c r="G5" t="n">
-        <v>32.40175269063025</v>
+        <v>32.78834590729745</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30319438737462</v>
+        <v>34.09851441260844</v>
       </c>
       <c r="I5" t="n">
-        <v>4.559471677374974</v>
+        <v>5.859843425822089</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660760106980248</v>
+        <v>4.63295032780006</v>
       </c>
       <c r="K5" t="n">
-        <v>14.15330598563973</v>
+        <v>12.32529125061199</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4465087751562</v>
+        <v>44.49218522916981</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8482862038024</v>
+        <v>99.80510608469278</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.30158337034005</v>
+        <v>86.31853705478464</v>
       </c>
       <c r="C6" t="n">
-        <v>41.41141715380118</v>
+        <v>42.54109603102935</v>
       </c>
       <c r="D6" t="n">
-        <v>2.051015395260415</v>
+        <v>2.074806221811605</v>
       </c>
       <c r="E6" t="n">
-        <v>7.431291873615173</v>
+        <v>8.005855823459054</v>
       </c>
       <c r="F6" t="n">
-        <v>0.74684365102908</v>
+        <v>0.7426725320949419</v>
       </c>
       <c r="G6" t="n">
-        <v>31.2445750275991</v>
+        <v>31.79813402261856</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35480794733767</v>
+        <v>34.16293647636732</v>
       </c>
       <c r="I6" t="n">
-        <v>3.805276656566869</v>
+        <v>4.892428652839776</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667772818931749</v>
+        <v>4.641703325593387</v>
       </c>
       <c r="K6" t="n">
-        <v>15.69841662965994</v>
+        <v>13.68146294521536</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76351422550069</v>
+        <v>43.61466759526024</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87334800896181</v>
+        <v>99.83722657150494</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.70315969932382</v>
+        <v>84.64087808460405</v>
       </c>
       <c r="C7" t="n">
-        <v>40.40381292323293</v>
+        <v>41.62331360936466</v>
       </c>
       <c r="D7" t="n">
-        <v>1.973040126302264</v>
+        <v>1.994892794938683</v>
       </c>
       <c r="E7" t="n">
-        <v>7.677956863886289</v>
+        <v>8.378098302742785</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477994064061476</v>
+        <v>0.7438668971069463</v>
       </c>
       <c r="G7" t="n">
-        <v>30.05672234405022</v>
+        <v>30.57339417404939</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39877269468278</v>
+        <v>34.21787726691952</v>
       </c>
       <c r="I7" t="n">
-        <v>3.175121973957701</v>
+        <v>4.083580541928312</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673746290038422</v>
+        <v>4.649168106918414</v>
       </c>
       <c r="K7" t="n">
-        <v>17.29684030067618</v>
+        <v>15.35912191539594</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19364464674181</v>
+        <v>42.88166367932719</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89429787065092</v>
+        <v>99.86409920408778</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.52253766730965</v>
+        <v>82.84374462443358</v>
       </c>
       <c r="C8" t="n">
-        <v>42.66053956364673</v>
+        <v>40.46028267282404</v>
       </c>
       <c r="D8" t="n">
-        <v>1.977259242740332</v>
+        <v>1.909952294319899</v>
       </c>
       <c r="E8" t="n">
-        <v>9.479460531955487</v>
+        <v>8.589309033149954</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493984883132442</v>
+        <v>0.7448868243593104</v>
       </c>
       <c r="G8" t="n">
-        <v>30.54564589426372</v>
+        <v>29.27161023190077</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47233046240922</v>
+        <v>34.26479392052827</v>
       </c>
       <c r="I8" t="n">
-        <v>5.614702495669865</v>
+        <v>3.407649667929693</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683740551957776</v>
+        <v>4.65554265224569</v>
       </c>
       <c r="K8" t="n">
-        <v>12.47746233269036</v>
+        <v>17.15625537556642</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67524071272931</v>
+        <v>42.2700291587782</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81324260906639</v>
+        <v>99.88656720716867</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.45228152579402</v>
+        <v>80.93468363909062</v>
       </c>
       <c r="C9" t="n">
-        <v>41.46132780682243</v>
+        <v>39.07998207448833</v>
       </c>
       <c r="D9" t="n">
-        <v>1.883239249555929</v>
+        <v>1.82040078825825</v>
       </c>
       <c r="E9" t="n">
-        <v>9.809951561792758</v>
+        <v>8.660422874537746</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507687602997646</v>
+        <v>0.7457590247624361</v>
       </c>
       <c r="G9" t="n">
-        <v>29.0931800988268</v>
+        <v>27.89915878957315</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53536297378916</v>
+        <v>34.30491513907205</v>
       </c>
       <c r="I9" t="n">
-        <v>4.687474129656093</v>
+        <v>2.843033118121769</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692304751873528</v>
+        <v>4.660993904765226</v>
       </c>
       <c r="K9" t="n">
-        <v>14.54771847420597</v>
+        <v>19.06531636090937</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83498976075855</v>
+        <v>41.76004462938204</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84403604178696</v>
+        <v>99.90534306477974</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.18552819764213</v>
+        <v>85.79177416001257</v>
       </c>
       <c r="C10" t="n">
-        <v>39.9214244158867</v>
+        <v>42.4776181185414</v>
       </c>
       <c r="D10" t="n">
-        <v>1.781364196001497</v>
+        <v>1.82239255302104</v>
       </c>
       <c r="E10" t="n">
-        <v>9.931334563870561</v>
+        <v>10.58234009432086</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519457566534395</v>
+        <v>0.7465749860368077</v>
       </c>
       <c r="G10" t="n">
-        <v>27.51936557614436</v>
+        <v>29.37278674661098</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5895048060582</v>
+        <v>35.7855518602558</v>
       </c>
       <c r="I10" t="n">
-        <v>3.912352319830068</v>
+        <v>2.816034257037033</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699660979083997</v>
+        <v>4.666093662730049</v>
       </c>
       <c r="K10" t="n">
-        <v>16.81447180235786</v>
+        <v>14.20822583998745</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13389616704276</v>
+        <v>43.22039082473679</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86979238528733</v>
+        <v>99.90623478326563</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.82537020631086</v>
+        <v>85.4466702070157</v>
       </c>
       <c r="C11" t="n">
-        <v>38.16723436798165</v>
+        <v>42.44670770000204</v>
       </c>
       <c r="D11" t="n">
-        <v>1.676453409853105</v>
+        <v>1.798579329882213</v>
       </c>
       <c r="E11" t="n">
-        <v>9.890557307539392</v>
+        <v>10.89945893313059</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529581717330103</v>
+        <v>0.7472791207030295</v>
       </c>
       <c r="G11" t="n">
-        <v>25.89865360529711</v>
+        <v>29.04142406898024</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63607589971846</v>
+        <v>35.87175496527409</v>
       </c>
       <c r="I11" t="n">
-        <v>3.264683238838487</v>
+        <v>2.417679284651591</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705988573331314</v>
+        <v>4.670494504393934</v>
       </c>
       <c r="K11" t="n">
-        <v>19.17462979368913</v>
+        <v>14.55332979298429</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54945938500059</v>
+        <v>42.91944913397926</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89132354667137</v>
+        <v>99.91948662696561</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.4078925355647</v>
+        <v>83.40525348323604</v>
       </c>
       <c r="C12" t="n">
-        <v>36.25457305129289</v>
+        <v>40.78111351845132</v>
       </c>
       <c r="D12" t="n">
-        <v>1.570095953906091</v>
+        <v>1.711991909382391</v>
       </c>
       <c r="E12" t="n">
-        <v>9.717034432979</v>
+        <v>10.7107952658335</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538300426866247</v>
+        <v>0.7478813133718247</v>
       </c>
       <c r="G12" t="n">
-        <v>24.25559278790539</v>
+        <v>27.64330836955255</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67618196358472</v>
+        <v>35.90066211289597</v>
       </c>
       <c r="I12" t="n">
-        <v>2.723719587711453</v>
+        <v>2.016356303625897</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711437766791404</v>
+        <v>4.674258208573904</v>
       </c>
       <c r="K12" t="n">
-        <v>21.59210746443531</v>
+        <v>16.59474651676398</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0626338387485</v>
+        <v>42.55698220687768</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90931435447672</v>
+        <v>99.93284224209299</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.98678349851339</v>
+        <v>84.49702565269779</v>
       </c>
       <c r="C13" t="n">
-        <v>34.25373856760797</v>
+        <v>41.71643202721641</v>
       </c>
       <c r="D13" t="n">
-        <v>1.464602005730952</v>
+        <v>1.713240074033012</v>
       </c>
       <c r="E13" t="n">
-        <v>9.442823258616047</v>
+        <v>11.32417171456062</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545813678065227</v>
+        <v>0.7484265723844962</v>
       </c>
       <c r="G13" t="n">
-        <v>22.62587185132268</v>
+        <v>27.96100793135313</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71074291910003</v>
+        <v>36.22438187665757</v>
       </c>
       <c r="I13" t="n">
-        <v>2.272028547146407</v>
+        <v>1.848131406305851</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716133548790767</v>
+        <v>4.6776660774031</v>
       </c>
       <c r="K13" t="n">
-        <v>24.01321650148659</v>
+        <v>15.50297434730223</v>
       </c>
       <c r="L13" t="n">
-        <v>41.657386053469</v>
+        <v>42.71903412655248</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92434112256356</v>
+        <v>99.93844050107111</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.0214784881689</v>
+        <v>82.3880155994807</v>
       </c>
       <c r="C14" t="n">
-        <v>38.70288086546518</v>
+        <v>39.89452115665664</v>
       </c>
       <c r="D14" t="n">
-        <v>1.466265400630639</v>
+        <v>1.626122115757806</v>
       </c>
       <c r="E14" t="n">
-        <v>11.89928140074587</v>
+        <v>11.00518452322893</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554383697727204</v>
+        <v>0.7488932169376852</v>
       </c>
       <c r="G14" t="n">
-        <v>24.62585178230633</v>
+        <v>26.53919556587292</v>
       </c>
       <c r="H14" t="n">
-        <v>36.72444802103038</v>
+        <v>36.24696780708696</v>
       </c>
       <c r="I14" t="n">
-        <v>2.828703702603452</v>
+        <v>1.541069764735846</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721489811079502</v>
+        <v>4.680582605860531</v>
       </c>
       <c r="K14" t="n">
-        <v>16.9785215118311</v>
+        <v>17.61198440051932</v>
       </c>
       <c r="L14" t="n">
-        <v>44.22441446607851</v>
+        <v>42.44215745931555</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90581684337479</v>
+        <v>99.94866301649152</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.24192172361172</v>
+        <v>81.37688418644576</v>
       </c>
       <c r="C15" t="n">
-        <v>38.36015570314886</v>
+        <v>39.09271269111164</v>
       </c>
       <c r="D15" t="n">
-        <v>1.437552124179329</v>
+        <v>1.583571188659286</v>
       </c>
       <c r="E15" t="n">
-        <v>12.05951386535697</v>
+        <v>10.93613816047723</v>
       </c>
       <c r="F15" t="n">
-        <v>0.75616081658195</v>
+        <v>0.7492961652310632</v>
       </c>
       <c r="G15" t="n">
-        <v>24.14361378516732</v>
+        <v>25.84474133956745</v>
       </c>
       <c r="H15" t="n">
-        <v>36.75956863623225</v>
+        <v>36.2664707929435</v>
       </c>
       <c r="I15" t="n">
-        <v>2.359507392456706</v>
+        <v>1.313565506873092</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726005103637188</v>
+        <v>4.683101032694144</v>
       </c>
       <c r="K15" t="n">
-        <v>17.75807827638828</v>
+        <v>18.62311581355423</v>
       </c>
       <c r="L15" t="n">
-        <v>43.80319091761275</v>
+        <v>42.24040952493456</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9214248971499</v>
+        <v>99.95623802960043</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.72356214763188</v>
+        <v>78.90387153692508</v>
       </c>
       <c r="C16" t="n">
-        <v>36.20619037536918</v>
+        <v>36.82317385814674</v>
       </c>
       <c r="D16" t="n">
-        <v>1.342475989947784</v>
+        <v>1.48217794354205</v>
       </c>
       <c r="E16" t="n">
-        <v>11.58990650648105</v>
+        <v>10.41844075509102</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567829786102045</v>
+        <v>0.7496428264912118</v>
       </c>
       <c r="G16" t="n">
-        <v>22.54681501421243</v>
+        <v>24.1899485443961</v>
       </c>
       <c r="H16" t="n">
-        <v>36.78981406455775</v>
+        <v>36.28324944609776</v>
       </c>
       <c r="I16" t="n">
-        <v>1.967873977508881</v>
+        <v>1.095144355736881</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729893616313778</v>
+        <v>4.685267665570072</v>
       </c>
       <c r="K16" t="n">
-        <v>20.27643785236812</v>
+        <v>21.0961284630749</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45182990025002</v>
+        <v>42.04420974803189</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93445812798731</v>
+        <v>99.96351206925354</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.49025641133217</v>
+        <v>83.80734789046438</v>
       </c>
       <c r="C17" t="n">
-        <v>37.49675206848495</v>
+        <v>40.09298358904605</v>
       </c>
       <c r="D17" t="n">
-        <v>1.343542396920096</v>
+        <v>1.482872945024696</v>
       </c>
       <c r="E17" t="n">
-        <v>12.39183074495198</v>
+        <v>12.14871973053095</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573841354658651</v>
+        <v>0.7499943381825958</v>
       </c>
       <c r="G17" t="n">
-        <v>23.03378064813388</v>
+        <v>25.73019639833816</v>
       </c>
       <c r="H17" t="n">
-        <v>37.28809374327974</v>
+        <v>37.8291679161041</v>
       </c>
       <c r="I17" t="n">
-        <v>1.941973895918949</v>
+        <v>1.178931948642644</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733650846661657</v>
+        <v>4.687464613641222</v>
       </c>
       <c r="K17" t="n">
-        <v>18.50974358866781</v>
+        <v>16.19265210953562</v>
       </c>
       <c r="L17" t="n">
-        <v>43.92882325960657</v>
+        <v>43.67508498808543</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93531891675934</v>
+        <v>99.9607206866671</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.07588355218616</v>
+        <v>85.44727889059236</v>
       </c>
       <c r="C18" t="n">
-        <v>35.38188366298122</v>
+        <v>40.81544538251118</v>
       </c>
       <c r="D18" t="n">
-        <v>1.256178311139898</v>
+        <v>1.484058011153779</v>
       </c>
       <c r="E18" t="n">
-        <v>11.85595244206007</v>
+        <v>12.74172285251285</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579011579195762</v>
+        <v>0.7505937104283205</v>
       </c>
       <c r="G18" t="n">
-        <v>21.53600492256032</v>
+        <v>25.87168924820132</v>
       </c>
       <c r="H18" t="n">
-        <v>37.31354817362571</v>
+        <v>37.85939981543113</v>
       </c>
       <c r="I18" t="n">
-        <v>1.619416307883237</v>
+        <v>2.048604562687957</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736882236997351</v>
+        <v>4.691210690177001</v>
       </c>
       <c r="K18" t="n">
-        <v>20.92411644781383</v>
+        <v>14.55272110940766</v>
       </c>
       <c r="L18" t="n">
-        <v>43.64005616987386</v>
+        <v>44.56360121845742</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94605628066891</v>
+        <v>99.93176771037625</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.12278324594929</v>
+        <v>82.69906272461719</v>
       </c>
       <c r="C19" t="n">
-        <v>34.67495575816586</v>
+        <v>38.38437606780558</v>
       </c>
       <c r="D19" t="n">
-        <v>1.222206515046623</v>
+        <v>1.383294912785856</v>
       </c>
       <c r="E19" t="n">
-        <v>11.76083955261178</v>
+        <v>12.16132232840483</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583387240143187</v>
+        <v>0.7511105537531841</v>
       </c>
       <c r="G19" t="n">
-        <v>20.95359017984032</v>
+        <v>24.11507896136079</v>
       </c>
       <c r="H19" t="n">
-        <v>37.33509074996922</v>
+        <v>37.88546901612664</v>
       </c>
       <c r="I19" t="n">
-        <v>1.353100499377545</v>
+        <v>1.708345991228494</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739617025089491</v>
+        <v>4.694440960957399</v>
       </c>
       <c r="K19" t="n">
-        <v>21.87721675405071</v>
+        <v>17.3009372753828</v>
       </c>
       <c r="L19" t="n">
-        <v>43.40275016271374</v>
+        <v>44.25778097451476</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9549226749303</v>
+        <v>99.94309431770313</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.60043777429023</v>
+        <v>79.90837615295634</v>
       </c>
       <c r="C20" t="n">
-        <v>32.36056012476751</v>
+        <v>35.85739046120332</v>
       </c>
       <c r="D20" t="n">
-        <v>1.13192859514554</v>
+        <v>1.28155002932002</v>
       </c>
       <c r="E20" t="n">
-        <v>11.08015274939551</v>
+        <v>11.50423719052113</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587159333630649</v>
+        <v>0.7515568701846369</v>
       </c>
       <c r="G20" t="n">
-        <v>19.40585948735289</v>
+        <v>22.34135314482342</v>
       </c>
       <c r="H20" t="n">
-        <v>37.35366179852734</v>
+        <v>37.90798089170968</v>
       </c>
       <c r="I20" t="n">
-        <v>1.128144626986721</v>
+        <v>1.424467587743477</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741974583519155</v>
+        <v>4.697230438653979</v>
       </c>
       <c r="K20" t="n">
-        <v>24.39956222570979</v>
+        <v>20.09162384704365</v>
       </c>
       <c r="L20" t="n">
-        <v>43.20229152454</v>
+        <v>44.00353163644112</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96241387501729</v>
+        <v>99.9525459446881</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.55749631159605</v>
+        <v>77.01278002161968</v>
       </c>
       <c r="C21" t="n">
-        <v>36.11951680255538</v>
+        <v>33.18094382403247</v>
       </c>
       <c r="D21" t="n">
-        <v>1.132645352603428</v>
+        <v>1.176513937652498</v>
       </c>
       <c r="E21" t="n">
-        <v>13.08889311034654</v>
+        <v>10.75929207759651</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591963658797353</v>
+        <v>0.7519432125314577</v>
       </c>
       <c r="G21" t="n">
-        <v>21.16165349862098</v>
+        <v>20.51025146076254</v>
       </c>
       <c r="H21" t="n">
-        <v>39.12082067964183</v>
+        <v>37.92746771816546</v>
       </c>
       <c r="I21" t="n">
-        <v>1.549310017755192</v>
+        <v>1.187666536589597</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744977286748345</v>
+        <v>4.699645078321609</v>
       </c>
       <c r="K21" t="n">
-        <v>18.44250368840395</v>
+        <v>22.98721997838032</v>
       </c>
       <c r="L21" t="n">
-        <v>45.38636852278296</v>
+        <v>43.79226765348322</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94838901374229</v>
+        <v>99.96043145589601</v>
       </c>
     </row>
   </sheetData>
